--- a/infos.xlsx
+++ b/infos.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daschultheiss/hero-database/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB4A4F4-7684-D04F-B295-5B84F7DBC5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Info" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Hearts" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Clubs" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Diamond" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Spade" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="Celestials" sheetId="6" r:id="rId10"/>
+    <sheet name="Info" sheetId="1" r:id="rId1"/>
+    <sheet name="Hearts" sheetId="2" r:id="rId2"/>
+    <sheet name="Clubs" sheetId="3" r:id="rId3"/>
+    <sheet name="Diamond" sheetId="4" r:id="rId4"/>
+    <sheet name="Spade" sheetId="5" r:id="rId5"/>
+    <sheet name="Celestials" sheetId="6" r:id="rId6"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -949,39 +958,45 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font/>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="15.0"/>
+      <sz val="15"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -992,7 +1007,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1026,7 +1041,13 @@
     </fill>
   </fills>
   <borders count="16">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -1040,6 +1061,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1051,6 +1073,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -1062,6 +1086,8 @@
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1070,9 +1096,11 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -1081,6 +1109,9 @@
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -1089,9 +1120,11 @@
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -1106,162 +1139,182 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="36">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="8" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="7" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="7" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="7" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="7" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="7" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
@@ -1272,11 +1325,17 @@
     <xdr:ext cx="4857750" cy="5610225"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
+        <xdr:cNvPr id="2" name="image1.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1293,32 +1352,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1508,22 +1543,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="B2:H39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="6.25"/>
-    <col customWidth="1" min="2" max="2" width="10.63"/>
-    <col customWidth="1" min="8" max="8" width="80.88"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="80.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1531,220 +1569,274 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4">
-        <v>320.0</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="C3" s="20">
+        <v>320</v>
+      </c>
+      <c r="H3" s="22" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="8" t="s">
+      <c r="C4" s="21"/>
+      <c r="H4" s="23"/>
+    </row>
+    <row r="5" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9">
-        <v>550.0</v>
-      </c>
-      <c r="H5" s="10"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="8" t="s">
+      <c r="C5" s="25">
+        <v>550</v>
+      </c>
+      <c r="H5" s="24"/>
+    </row>
+    <row r="6" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="6"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="11" t="s">
+      <c r="C6" s="21"/>
+    </row>
+    <row r="7" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="12">
-        <v>1600.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="11" t="s">
+      <c r="C7" s="26">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="H8" s="13" t="s">
+      <c r="C8" s="21"/>
+      <c r="H8" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9">
-      <c r="H9" s="14" t="s">
+    <row r="9" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H9" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="15" t="s">
+    <row r="10" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B10" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="17"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="H11" s="20" t="s">
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="29"/>
+    </row>
+    <row r="11" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="30"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="32"/>
+      <c r="H11" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="18"/>
-      <c r="F12" s="19"/>
-      <c r="H12" s="20" t="s">
+    <row r="12" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="30"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="32"/>
+      <c r="H12" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="18"/>
-      <c r="F13" s="19"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="18"/>
-      <c r="F14" s="19"/>
-      <c r="H14" s="20" t="s">
+    <row r="13" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="32"/>
+    </row>
+    <row r="14" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="32"/>
+      <c r="H14" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="18"/>
-      <c r="F15" s="19"/>
-      <c r="H15" s="20" t="s">
+    <row r="15" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15" s="30"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="32"/>
+      <c r="H15" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="18"/>
-      <c r="F16" s="19"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="18"/>
-      <c r="F17" s="19"/>
-      <c r="H17" s="20" t="s">
+    <row r="16" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="32"/>
+    </row>
+    <row r="17" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="32"/>
+      <c r="H17" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="18"/>
-      <c r="F18" s="19"/>
-      <c r="H18" s="20" t="s">
+    <row r="18" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="32"/>
+      <c r="H18" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="18"/>
-      <c r="F19" s="19"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="18"/>
-      <c r="F20" s="19"/>
-      <c r="H20" s="20" t="s">
+    <row r="19" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="32"/>
+    </row>
+    <row r="20" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="30"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="32"/>
+      <c r="H20" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="18"/>
-      <c r="F21" s="19"/>
-      <c r="H21" s="20" t="s">
+    <row r="21" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="30"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="32"/>
+      <c r="H21" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="18"/>
-      <c r="F22" s="19"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="18"/>
-      <c r="F23" s="19"/>
-      <c r="H23" s="20" t="s">
+    <row r="22" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="32"/>
+    </row>
+    <row r="23" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="32"/>
+      <c r="H23" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="18"/>
-      <c r="F24" s="19"/>
-      <c r="H24" s="20" t="s">
+    <row r="24" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="30"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="32"/>
+      <c r="H24" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="18"/>
-      <c r="F25" s="19"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="18"/>
-      <c r="F26" s="19"/>
-      <c r="H26" s="20" t="s">
+    <row r="25" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="32"/>
+    </row>
+    <row r="26" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="30"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="32"/>
+      <c r="H26" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="18"/>
-      <c r="F27" s="19"/>
-      <c r="H27" s="20" t="s">
+    <row r="27" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="30"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="32"/>
+      <c r="H27" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="18"/>
-      <c r="F28" s="19"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="21"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="23"/>
-      <c r="H29" s="20" t="s">
+    <row r="28" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="30"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="32"/>
+    </row>
+    <row r="29" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="33"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="35"/>
+      <c r="H29" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30">
-      <c r="H30" s="20" t="s">
+    <row r="30" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H30" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32">
-      <c r="H32" s="20" t="s">
+    <row r="32" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H32" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33">
-      <c r="H33" s="20" t="s">
+    <row r="33" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H33" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35">
-      <c r="H35" s="20" t="s">
+    <row r="35" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H35" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36">
-      <c r="H36" s="20" t="s">
+    <row r="36" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H36" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="38">
-      <c r="H38" s="20" t="s">
+    <row r="38" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H38" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="39">
-      <c r="H39" s="20" t="s">
+    <row r="39" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H39" s="7" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1756,1789 +1848,1795 @@
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="B10:F29"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="20.38"/>
-    <col customWidth="1" min="3" max="3" width="23.5"/>
-    <col customWidth="1" min="4" max="4" width="115.63"/>
-    <col customWidth="1" min="5" max="5" width="9.75"/>
-    <col customWidth="1" min="6" max="6" width="8.5"/>
-    <col customWidth="1" min="7" max="7" width="8.75"/>
-    <col customWidth="1" min="8" max="8" width="10.63"/>
-    <col customWidth="1" min="9" max="9" width="32.88"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23.5" customWidth="1"/>
+    <col min="4" max="4" width="115.6640625" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="6" max="6" width="8.5" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="32.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="26" t="s">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="I2" s="10" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="26" t="s">
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="I3" s="10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="26" t="s">
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="26" t="s">
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="H5" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="26" t="s">
+      <c r="I5" s="10" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="26" t="s">
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="H6" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="26" t="s">
+      <c r="I6" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="26" t="s">
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I7" s="26" t="s">
+      <c r="I7" s="10" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="26" t="s">
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="H8" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="I8" s="26" t="s">
+      <c r="I8" s="10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="26" t="s">
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="H9" s="26" t="s">
+      <c r="H9" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="I9" s="26" t="s">
+      <c r="I9" s="10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="26" t="s">
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="26">
-        <v>1.0</v>
-      </c>
-      <c r="C10" s="26" t="s">
+      <c r="B10" s="10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="H10" s="26" t="s">
+      <c r="H10" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="I10" s="26" t="s">
+      <c r="I10" s="10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="26" t="s">
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="26">
-        <v>0.0</v>
-      </c>
-      <c r="C11" s="26" t="s">
+      <c r="B11" s="10">
+        <v>0</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="I11" s="26" t="s">
+      <c r="I11" s="10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="26" t="s">
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="26">
-        <v>0.0</v>
-      </c>
-      <c r="C12" s="26" t="s">
+      <c r="B12" s="10">
+        <v>0</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="G12" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="H12" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="I12" s="26" t="s">
+      <c r="I12" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="26" t="s">
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="26">
-        <v>0.0</v>
-      </c>
-      <c r="C13" s="26" t="s">
+      <c r="B13" s="10">
+        <v>0</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="F13" s="26" t="s">
+      <c r="F13" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="I13" s="26" t="s">
+      <c r="I13" s="10" t="s">
         <v>103</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.63"/>
-    <col customWidth="1" min="2" max="2" width="24.0"/>
-    <col customWidth="1" min="3" max="3" width="22.38"/>
-    <col customWidth="1" min="4" max="4" width="79.75"/>
-    <col customWidth="1" min="9" max="9" width="26.5"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" customWidth="1"/>
+    <col min="4" max="4" width="79.6640625" customWidth="1"/>
+    <col min="9" max="9" width="26.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="A1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="28" t="s">
+    <row r="2" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="A2" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="I2" s="12" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="28" t="s">
+    <row r="3" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="A3" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="I3" s="28" t="s">
+      <c r="I3" s="12" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="28" t="s">
+    <row r="4" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="A4" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="28">
-        <v>30.0</v>
-      </c>
-      <c r="C4" s="28" t="s">
+      <c r="B4" s="12">
+        <v>30</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="12" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="28" t="s">
+    <row r="5" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="A5" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B5" s="28">
-        <v>20.0</v>
-      </c>
-      <c r="C5" s="28" t="s">
+      <c r="B5" s="12">
+        <v>20</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="I5" s="28" t="s">
+      <c r="I5" s="12" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="28" t="s">
+    <row r="6" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="A6" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="I6" s="12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="7" ht="28.5" customHeight="1">
-      <c r="A7" s="28" t="s">
+    <row r="7" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B7" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="C7" s="28" t="s">
+      <c r="B7" s="12">
+        <v>0</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="I7" s="28" t="s">
+      <c r="I7" s="12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="28" t="s">
+    <row r="8" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="A8" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="G8" s="28" t="s">
+      <c r="G8" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="H8" s="28" t="s">
+      <c r="H8" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="I8" s="28" t="s">
+      <c r="I8" s="12" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="28" t="s">
+    <row r="9" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="A9" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="C9" s="28" t="s">
+      <c r="B9" s="12">
+        <v>0</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="G9" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="I9" s="28" t="s">
+      <c r="I9" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="28" t="s">
+    <row r="10" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="A10" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B10" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="C10" s="28" t="s">
+      <c r="B10" s="12">
+        <v>0</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="28" t="s">
+      <c r="G10" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="I10" s="28" t="s">
+      <c r="I10" s="12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="28" t="s">
+    <row r="11" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="A11" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B11" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="C11" s="28" t="s">
+      <c r="B11" s="12">
+        <v>0</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="G11" s="28" t="s">
+      <c r="G11" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="H11" s="28" t="s">
+      <c r="H11" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="I11" s="28" t="s">
+      <c r="I11" s="12" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="28" t="s">
+    <row r="12" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="A12" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B12" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="C12" s="28" t="s">
+      <c r="B12" s="12">
+        <v>0</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="G12" s="28" t="s">
+      <c r="G12" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="H12" s="28" t="s">
+      <c r="H12" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="I12" s="28" t="s">
+      <c r="I12" s="12" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="28" t="s">
+    <row r="13" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="A13" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B13" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="C13" s="28" t="s">
+      <c r="B13" s="12">
+        <v>0</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="G13" s="28" t="s">
+      <c r="G13" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="H13" s="28" t="s">
+      <c r="H13" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="I13" s="28" t="s">
+      <c r="I13" s="12" t="s">
         <v>143</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.88"/>
-    <col customWidth="1" min="2" max="2" width="20.75"/>
-    <col customWidth="1" min="3" max="3" width="21.25"/>
-    <col customWidth="1" min="4" max="4" width="58.25"/>
-    <col customWidth="1" min="9" max="9" width="30.75"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.1640625" customWidth="1"/>
+    <col min="4" max="4" width="58.1640625" customWidth="1"/>
+    <col min="9" max="9" width="30.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="I1" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="30" t="s">
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="I3" s="14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="30" t="s">
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="30" t="s">
+      <c r="H4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="14" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="30" t="s">
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G5" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="H5" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="I5" s="30" t="s">
+      <c r="I5" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="30" t="s">
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="B6" s="30">
-        <v>20.0</v>
-      </c>
-      <c r="C6" s="30" t="s">
+      <c r="B6" s="14">
+        <v>20</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="I6" s="30" t="s">
+      <c r="I6" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="30" t="s">
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="B7" s="30">
-        <v>10.0</v>
-      </c>
-      <c r="C7" s="30" t="s">
+      <c r="B7" s="14">
+        <v>10</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="H7" s="30" t="s">
+      <c r="H7" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="I7" s="30" t="s">
+      <c r="I7" s="14" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="30" t="s">
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="30" t="s">
+      <c r="H8" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="I8" s="30" t="s">
+      <c r="I8" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="30" t="s">
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="B9" s="30">
-        <v>0.0</v>
-      </c>
-      <c r="C9" s="30" t="s">
+      <c r="B9" s="14">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="D9" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="F9" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="30" t="s">
+      <c r="G9" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="H9" s="30" t="s">
+      <c r="H9" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="I9" s="30" t="s">
+      <c r="I9" s="14" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="30" t="s">
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="H10" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="I10" s="14" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="30" t="s">
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="F11" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="30" t="s">
+      <c r="G11" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="H11" s="30" t="s">
+      <c r="H11" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="I11" s="30" t="s">
+      <c r="I11" s="14" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="30" t="s">
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="B12" s="30">
-        <v>0.0</v>
-      </c>
-      <c r="C12" s="30" t="s">
+      <c r="B12" s="14">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="H12" s="30" t="s">
+      <c r="H12" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="I12" s="30" t="s">
+      <c r="I12" s="14" t="s">
         <v>176</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="22.63"/>
-    <col customWidth="1" min="3" max="3" width="15.88"/>
-    <col customWidth="1" min="4" max="4" width="64.0"/>
-    <col customWidth="1" min="5" max="8" width="13.63"/>
-    <col customWidth="1" min="9" max="9" width="21.13"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="64" customWidth="1"/>
+    <col min="5" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="21.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="16" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="I3" s="16" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="32" t="s">
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="32" t="s">
+      <c r="I4" s="16" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="32" t="s">
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="I5" s="32" t="s">
+      <c r="I5" s="16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="32" t="s">
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="H6" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="I6" s="32" t="s">
+      <c r="I6" s="16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="32" t="s">
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="32" t="s">
+      <c r="H7" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="I7" s="32" t="s">
+      <c r="I7" s="16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="32" t="s">
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="B8" s="32">
-        <v>1.0</v>
-      </c>
-      <c r="C8" s="32" t="s">
+      <c r="B8" s="16">
+        <v>1</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="I8" s="32" t="s">
+      <c r="I8" s="16" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="32" t="s">
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="32" t="s">
+      <c r="I9" s="16" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="32" t="s">
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="B10" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="C10" s="32" t="s">
+      <c r="B10" s="16">
+        <v>0</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="H10" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="I10" s="32" t="s">
+      <c r="I10" s="16" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="B11" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="C11" s="32" t="s">
+      <c r="B11" s="16">
+        <v>0</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="F11" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="G11" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="H11" s="32" t="s">
+      <c r="H11" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="I11" s="32" t="s">
+      <c r="I11" s="16" t="s">
         <v>212</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="20.25"/>
-    <col customWidth="1" min="3" max="3" width="24.13"/>
-    <col customWidth="1" min="4" max="4" width="123.25"/>
-    <col customWidth="1" min="5" max="5" width="9.0"/>
-    <col customWidth="1" min="6" max="6" width="8.88"/>
-    <col customWidth="1" min="7" max="7" width="10.0"/>
-    <col customWidth="1" min="8" max="8" width="9.75"/>
-    <col customWidth="1" min="9" max="9" width="35.25"/>
+    <col min="2" max="2" width="20.1640625" customWidth="1"/>
+    <col min="3" max="3" width="24.1640625" customWidth="1"/>
+    <col min="4" max="4" width="123.1640625" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" customWidth="1"/>
+    <col min="9" max="9" width="35.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="18" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="35" t="s">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="H2" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="35" t="s">
+      <c r="I2" s="19" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="35" t="s">
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="I3" s="35" t="s">
+      <c r="I3" s="19" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="35" t="s">
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="B4" s="35">
-        <v>30.0</v>
-      </c>
-      <c r="C4" s="35" t="s">
+      <c r="B4" s="19">
+        <v>30</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="19" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="35" t="s">
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="G5" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="35" t="s">
+      <c r="H5" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="I5" s="35" t="s">
+      <c r="I5" s="19" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="35" t="s">
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="B6" s="35">
-        <v>30.0</v>
-      </c>
-      <c r="C6" s="35" t="s">
+      <c r="B6" s="19">
+        <v>30</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="35" t="s">
+      <c r="H6" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="I6" s="35" t="s">
+      <c r="I6" s="19" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="35" t="s">
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="B7" s="35">
-        <v>30.0</v>
-      </c>
-      <c r="C7" s="35" t="s">
+      <c r="B7" s="19">
+        <v>30</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="35" t="s">
+      <c r="G7" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="35" t="s">
+      <c r="H7" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="I7" s="35" t="s">
+      <c r="I7" s="19" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="35" t="s">
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="B8" s="35">
-        <v>30.0</v>
-      </c>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="19">
+        <v>30</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="I8" s="35" t="s">
+      <c r="I8" s="19" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="35" t="s">
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G9" s="35" t="s">
+      <c r="G9" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="19" t="s">
         <v>245</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>